--- a/pensum/ok09/LOM_Ovingsark_Okonomistyring_kap09_Delbudsjetter_NY.xlsx
+++ b/pensum/ok09/LOM_Ovingsark_Okonomistyring_kap09_Delbudsjetter_NY.xlsx
@@ -5459,7 +5459,7 @@
       </c>
       <c r="O28" s="31" t="inlineStr">
         <is>
-          <t>Forskuddstrekket settes straks inn på skattetrekkskonto og er låst. Kontoen tappes derfor på utlønningsdagen, ikke når skatten betales videre.</t>
+          <t>Forskuddstrekket betales til Skatteetaten senest første virkedag etter lønnsutbetalingen (skattetrekkskontoen ble avviklet 1.1.2026). Pengene forlater derfor kassen samme måned som lønna, ikke ved neste termin.</t>
         </is>
       </c>
     </row>

--- a/pensum/ok09/LOM_Ovingsark_Okonomistyring_kap09_Delbudsjetter_NY.xlsx
+++ b/pensum/ok09/LOM_Ovingsark_Okonomistyring_kap09_Delbudsjetter_NY.xlsx
@@ -804,7 +804,7 @@
     <row r="22" ht="15" customHeight="1" s="25">
       <c r="A22" s="28" t="inlineStr">
         <is>
-          <t>Tallene som ligger inne er budsjettet Nordlys Elektro AS har lagt for 2027, og budsjettkontrollen for 2026. Samme bedrift som i alle ti kapitlene i Bok 1.</t>
+          <t xml:space="preserve">Tallene som ligger inne er budsjettet Nordlys Elektro AS har lagt for 2027, og budsjettkontrollen for 2026. Samme bedrift som i alle ti kapitlene i Økonomistyring for LØM-emnet.</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
     <row r="73" ht="15" customHeight="1" s="25">
       <c r="A73" s="28" t="inlineStr">
         <is>
-          <t>Nordlys Elektro AS er en konstruert casebedrift. Tallene henger sammen på tvers av alle ti kapitlene i Bok 1.</t>
+          <t xml:space="preserve">Nordlys Elektro AS er en konstruert casebedrift. Tallene henger sammen på tvers av alle ti kapitlene i Økonomistyring for LØM-emnet.</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
     <row r="42" ht="15" customHeight="1" s="25">
       <c r="A42" s="28" t="inlineStr">
         <is>
-          <t>Kilde: Bok 1 kap. 9.2. Nøkkeltallene er de samme som i kapittel 4.</t>
+          <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 9.2. Nøkkeltallene er de samme som i kapittel 4.</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
     <row r="34" ht="15" customHeight="1" s="25">
       <c r="A34" s="28" t="inlineStr">
         <is>
-          <t>Kilde: Bok 1 kap. 9.8 og 9.9. Tallene er de samme som i arbeidsboka «Budsjett».</t>
+          <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 9.8 og 9.9. Tallene er de samme som i arbeidsboka «Budsjett».</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
     <row r="42" ht="15" customHeight="1" s="25">
       <c r="A42" s="28" t="inlineStr">
         <is>
-          <t>Kilde: Bok 1 kap. 9.6 og 9.7. Bransjetall: NHO Elektro, Lønnsomhetsrapport 2025, gjengitt i Elektro 24-7 19.08.2026 (hentet 10.09.2026). De 809 er bedriftene i datagrunnlaget, ikke bransjen. NHO Elektro oppgir ikke svarprosent.</t>
+          <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 9.6 og 9.7. Bransjetall: NHO Elektro, Lønnsomhetsrapport 2025, gjengitt i Elektro 24-7 19.08.2026 (hentet 10.09.2026). De 809 er bedriftene i datagrunnlaget, ikke bransjen. NHO Elektro oppgir ikke svarprosent.</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
     <row r="30" ht="15" customHeight="1" s="25">
       <c r="A30" s="28" t="inlineStr">
         <is>
-          <t>Kilde: Bok 1 kap. 9.2. Timepris og materiellpåslag er de samme som i kapittel 5. Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet (ISBN 978-82-450-5544-3), kapittel 9 «Budsjettering og budsjettkontroll»</t>
+          <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 9.2. Timepris og materiellpåslag er de samme som i kapittel 5. Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet (ISBN 978-82-450-5544-3), kapittel 9 «Budsjettering og budsjettkontroll»</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
     <row r="32" ht="15" customHeight="1" s="25">
       <c r="A32" s="28" t="inlineStr">
         <is>
-          <t>Kilde: Bok 1 kap. 9.4.3. Materiellpåslaget står i kapittel 5.</t>
+          <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 9.4.3. Materiellpåslaget står i kapittel 5.</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
     <row r="45" ht="15" customHeight="1" s="25">
       <c r="A45" s="28" t="inlineStr">
         <is>
-          <t>Kilde: Bok 1 kap. 9.4.4 til 9.4.6. Forfallsreglene følger skattebetalingsloven (Lovdata).</t>
+          <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 9.4.4 til 9.4.6. Forfallsreglene følger skattebetalingsloven (Lovdata).</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
     <row r="27" ht="15" customHeight="1" s="25">
       <c r="A27" s="28" t="inlineStr">
         <is>
-          <t>Kilde: Bok 1 kap. 9.2 og kap. 9.4.8. Delingen i faste og variable er den samme som i kapittel 2 og kapittel 8.</t>
+          <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 9.2 og kap. 9.4.8. Delingen i faste og variable er den samme som i kapittel 2 og kapittel 8.</t>
         </is>
       </c>
     </row>
@@ -7552,7 +7552,7 @@
     <row r="52" ht="15" customHeight="1" s="25">
       <c r="A52" s="28" t="inlineStr">
         <is>
-          <t>Kilde: Bok 1 kap. 9.4.9 til 9.4.16. Avdragsplanen er lånet på 2 800 000 kroner nedbetalt over fem år.</t>
+          <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 9.4.9 til 9.4.16. Avdragsplanen er lånet på 2 800 000 kroner nedbetalt over fem år.</t>
         </is>
       </c>
     </row>
@@ -8189,7 +8189,7 @@
     <row r="30" ht="15" customHeight="1" s="25">
       <c r="A30" s="28" t="inlineStr">
         <is>
-          <t>Kilde: Bok 1 kap. 9.4.7. Terminene og forfallsfristene følger merverdiavgiftsloven og skattebetalingsloven (Lovdata). Alminnelig sats er 25 prosent; næringsmidler 15 prosent og persontransport, overnatting og kino 12 prosent.</t>
+          <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 9.4.7. Terminene og forfallsfristene følger merverdiavgiftsloven og skattebetalingsloven (Lovdata). Alminnelig sats er 25 prosent; næringsmidler 15 prosent og persontransport, overnatting og kino 12 prosent.</t>
         </is>
       </c>
     </row>
@@ -9300,7 +9300,7 @@
     <row r="33" ht="15" customHeight="1" s="25">
       <c r="A33" s="28" t="inlineStr">
         <is>
-          <t>Kilde: Bok 1 kap. 9.2 og 9.3.</t>
+          <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 9.2 og 9.3.</t>
         </is>
       </c>
     </row>
@@ -11624,7 +11624,7 @@
     <row r="85" ht="15" customHeight="1" s="25">
       <c r="A85" s="28" t="inlineStr">
         <is>
-          <t>Kilde: Bok 1 kap. 9.4 og 9.6. Oppstillingen i tre nivåer — drift, finansiering og investering — er den samme som brukes i 3EKC.</t>
+          <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 9.4 og 9.6. Oppstillingen i tre nivåer — drift, finansiering og investering — er den samme som brukes i 3EKC.</t>
         </is>
       </c>
     </row>
